--- a/trimestre 2/CostosFichas.xlsx
+++ b/trimestre 2/CostosFichas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aprendiz\Desktop\XD\RoyalPets\trimestre 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E19219F-EDA0-469F-9411-7345D32BBC55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3048A71D-225E-44A5-873A-4CCCCAFBBF34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E11BA5A1-A161-48B3-A771-26A7DBB69ABE}"/>
   </bookViews>
@@ -536,9 +536,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -572,27 +569,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -601,17 +580,11 @@
     </xf>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -619,26 +592,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1042,7 +1042,7 @@
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="2:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1148,291 +1148,291 @@
       <c r="E7" s="1"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
       <c r="E8" s="1"/>
     </row>
     <row r="9" spans="2:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="17" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="19">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="20">
         <f>E$3*C10</f>
         <v>255000.00000000003</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="20">
         <f>E$4*C10</f>
         <v>238000.00000000003</v>
       </c>
-      <c r="F10" s="21">
+      <c r="F10" s="20">
         <f>E$5*C10</f>
         <v>297500</v>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="20">
         <f>E$6*C10</f>
         <v>153000</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="21">
         <v>0.12</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="20">
         <f t="shared" ref="D11:D19" si="0">E$3*C11</f>
         <v>360000</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="20">
         <f t="shared" ref="E11:E19" si="1">E$4*C11</f>
         <v>336000</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="20">
         <f t="shared" ref="F11:F19" si="2">E$5*C11</f>
         <v>420000</v>
       </c>
-      <c r="G11" s="21">
+      <c r="G11" s="20">
         <f t="shared" ref="G11:G19" si="3">E$6*C11</f>
         <v>216000</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="23">
+      <c r="C12" s="22">
         <v>5.2199999999999998E-3</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="20">
         <f t="shared" si="0"/>
         <v>15660</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="20">
         <f t="shared" si="1"/>
         <v>14616</v>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="20">
         <f t="shared" si="2"/>
         <v>18270</v>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="20">
         <f t="shared" si="3"/>
         <v>9396</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="24">
         <v>0.04</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="20">
         <f t="shared" si="0"/>
         <v>120000</v>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="20">
         <f t="shared" si="1"/>
         <v>112000</v>
       </c>
-      <c r="F13" s="21">
+      <c r="F13" s="20">
         <f t="shared" si="2"/>
         <v>140000</v>
       </c>
-      <c r="G13" s="21">
+      <c r="G13" s="20">
         <f t="shared" si="3"/>
         <v>72000</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="21">
         <v>0.02</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="20">
         <f t="shared" si="0"/>
         <v>60000</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="20">
         <f t="shared" si="1"/>
         <v>56000</v>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="20">
         <f t="shared" si="2"/>
         <v>70000</v>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="20">
         <f t="shared" si="3"/>
         <v>36000</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="21">
         <v>0.03</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="20">
         <f t="shared" si="0"/>
         <v>90000</v>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="20">
         <f t="shared" si="1"/>
         <v>84000</v>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="20">
         <f t="shared" si="2"/>
         <v>105000</v>
       </c>
-      <c r="G15" s="21">
+      <c r="G15" s="20">
         <f t="shared" si="3"/>
         <v>54000</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="25">
         <v>8.3299999999999999E-2</v>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="20">
         <f>E$3*C16</f>
         <v>249900</v>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="20">
         <f t="shared" si="1"/>
         <v>233240</v>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="20">
         <f t="shared" si="2"/>
         <v>291550</v>
       </c>
-      <c r="G16" s="21">
+      <c r="G16" s="20">
         <f t="shared" si="3"/>
         <v>149940</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="26">
         <v>8.3299999999999999E-2</v>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="20">
         <f t="shared" si="0"/>
         <v>249900</v>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="20">
         <f t="shared" si="1"/>
         <v>233240</v>
       </c>
-      <c r="F17" s="21">
+      <c r="F17" s="20">
         <f t="shared" si="2"/>
         <v>291550</v>
       </c>
-      <c r="G17" s="21">
+      <c r="G17" s="20">
         <f t="shared" si="3"/>
         <v>149940</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="22">
+      <c r="C18" s="21">
         <v>0.01</v>
       </c>
-      <c r="D18" s="21">
+      <c r="D18" s="20">
         <f t="shared" si="0"/>
         <v>30000</v>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="20">
         <f t="shared" si="1"/>
         <v>28000</v>
       </c>
-      <c r="F18" s="21">
+      <c r="F18" s="20">
         <f t="shared" si="2"/>
         <v>35000</v>
       </c>
-      <c r="G18" s="21">
+      <c r="G18" s="20">
         <f t="shared" si="3"/>
         <v>18000</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="26">
         <v>4.1700000000000001E-2</v>
       </c>
-      <c r="D19" s="21">
+      <c r="D19" s="20">
         <f t="shared" si="0"/>
         <v>125100</v>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="20">
         <f t="shared" si="1"/>
         <v>116760</v>
       </c>
-      <c r="F19" s="21">
+      <c r="F19" s="20">
         <f t="shared" si="2"/>
         <v>145950</v>
       </c>
-      <c r="G19" s="21">
+      <c r="G19" s="20">
         <f t="shared" si="3"/>
         <v>75060</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="21">
+      <c r="C20" s="26"/>
+      <c r="D20" s="20">
         <f>SUM(D10:D19)</f>
         <v>1555560</v>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="20">
         <f t="shared" ref="E20" si="4">SUM(E10:E19)</f>
         <v>1451856</v>
       </c>
-      <c r="F20" s="21">
+      <c r="F20" s="20">
         <f>SUM(F10+F11+F12+F13+F14+F15+F16+F17+F19+F18)</f>
         <v>1814820</v>
       </c>
-      <c r="G20" s="21">
+      <c r="G20" s="20">
         <f>SUM(G10+G11+G12+G13+G14+G15+G16+G17+G19+G18)</f>
         <v>933336</v>
       </c>
@@ -1451,409 +1451,393 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="4" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="J4" s="30" t="s">
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="J4" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="Q4" s="31" t="s">
+      <c r="K4" s="48"/>
+      <c r="L4" s="48"/>
+      <c r="M4" s="48"/>
+      <c r="N4" s="48"/>
+      <c r="Q4" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="R4" s="31"/>
-      <c r="S4" s="31"/>
-      <c r="T4" s="31"/>
-      <c r="U4" s="31"/>
+      <c r="R4" s="49"/>
+      <c r="S4" s="49"/>
+      <c r="T4" s="49"/>
+      <c r="U4" s="49"/>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="E5" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="J5" s="34" t="s">
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="J5" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="K5" s="34" t="s">
+      <c r="K5" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="L5" s="35" t="s">
+      <c r="L5" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="M5" s="35"/>
-      <c r="N5" s="35"/>
-      <c r="Q5" s="36" t="s">
+      <c r="M5" s="51"/>
+      <c r="N5" s="51"/>
+      <c r="Q5" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="R5" s="36" t="s">
+      <c r="R5" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="S5" s="37" t="s">
+      <c r="S5" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="T5" s="37"/>
-      <c r="U5" s="37"/>
+      <c r="T5" s="52"/>
+      <c r="U5" s="52"/>
     </row>
     <row r="6" spans="2:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="39" t="s">
+      <c r="C6" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="40">
+      <c r="D6" s="33">
         <v>1196883</v>
       </c>
-      <c r="E6" s="41" t="s">
+      <c r="E6" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="I6" s="42" t="s">
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="I6" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="39" t="s">
+      <c r="J6" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="K6" s="43">
+      <c r="K6" s="35">
         <v>1196883</v>
       </c>
-      <c r="L6" s="44" t="s">
+      <c r="L6" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="M6" s="44"/>
-      <c r="N6" s="44"/>
-      <c r="P6" s="45" t="s">
+      <c r="M6" s="43"/>
+      <c r="N6" s="43"/>
+      <c r="P6" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="Q6" s="39" t="s">
+      <c r="Q6" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="R6" s="46">
+      <c r="R6" s="37">
         <v>1213134</v>
       </c>
-      <c r="S6" s="44" t="s">
+      <c r="S6" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="44"/>
-      <c r="U6" s="44"/>
+      <c r="T6" s="43"/>
+      <c r="U6" s="43"/>
     </row>
     <row r="7" spans="2:21" ht="75" x14ac:dyDescent="0.25">
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="39" t="s">
+      <c r="C7" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="40">
+      <c r="D7" s="33">
         <v>1834000</v>
       </c>
-      <c r="E7" s="44" t="s">
+      <c r="E7" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="I7" s="42" t="s">
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="I7" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="J7" s="47" t="s">
+      <c r="J7" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="K7" s="39" t="s">
+      <c r="K7" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="L7" s="48" t="s">
+      <c r="L7" s="54" t="s">
         <v>46</v>
       </c>
-      <c r="M7" s="48"/>
-      <c r="N7" s="48"/>
-      <c r="P7" s="45" t="s">
+      <c r="M7" s="54"/>
+      <c r="N7" s="54"/>
+      <c r="P7" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="Q7" s="39" t="s">
+      <c r="Q7" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="R7" s="39" t="s">
+      <c r="R7" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="S7" s="48" t="s">
+      <c r="S7" s="54" t="s">
         <v>46</v>
       </c>
-      <c r="T7" s="48"/>
-      <c r="U7" s="48"/>
+      <c r="T7" s="54"/>
+      <c r="U7" s="54"/>
     </row>
     <row r="8" spans="2:21" ht="75" x14ac:dyDescent="0.25">
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="39" t="s">
+      <c r="C8" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="43">
+      <c r="D8" s="35">
         <v>1600000</v>
       </c>
-      <c r="E8" s="44" t="s">
+      <c r="E8" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="I8" s="42" t="s">
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="I8" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="J8" s="39" t="s">
+      <c r="J8" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="K8" s="43">
+      <c r="K8" s="35">
         <v>1600000</v>
       </c>
-      <c r="L8" s="44" t="s">
+      <c r="L8" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="M8" s="44"/>
-      <c r="N8" s="44"/>
-      <c r="P8" s="45" t="s">
+      <c r="M8" s="43"/>
+      <c r="N8" s="43"/>
+      <c r="P8" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="Q8" s="39" t="s">
+      <c r="Q8" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="R8" s="46">
+      <c r="R8" s="37">
         <v>1600000</v>
       </c>
-      <c r="S8" s="44" t="s">
+      <c r="S8" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="T8" s="44"/>
-      <c r="U8" s="44"/>
+      <c r="T8" s="43"/>
+      <c r="U8" s="43"/>
     </row>
     <row r="9" spans="2:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="43">
+      <c r="D9" s="35">
         <v>996959</v>
       </c>
-      <c r="E9" s="49" t="s">
+      <c r="E9" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="50"/>
-      <c r="G9" s="51"/>
-      <c r="I9" s="42" t="s">
+      <c r="F9" s="45"/>
+      <c r="G9" s="46"/>
+      <c r="I9" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="J9" s="39" t="s">
+      <c r="J9" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="K9" s="43">
+      <c r="K9" s="35">
         <v>996959</v>
       </c>
-      <c r="L9" s="44" t="s">
+      <c r="L9" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="M9" s="44"/>
-      <c r="N9" s="44"/>
-      <c r="P9" s="45" t="s">
+      <c r="M9" s="43"/>
+      <c r="N9" s="43"/>
+      <c r="P9" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="Q9" s="39" t="s">
+      <c r="Q9" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="R9" s="46">
+      <c r="R9" s="37">
         <v>996959</v>
       </c>
-      <c r="S9" s="44" t="s">
+      <c r="S9" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="T9" s="44"/>
-      <c r="U9" s="44"/>
+      <c r="T9" s="43"/>
+      <c r="U9" s="43"/>
     </row>
     <row r="10" spans="2:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="43">
+      <c r="D10" s="35">
         <v>650000</v>
       </c>
-      <c r="E10" s="44" t="s">
+      <c r="E10" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="I10" s="42" t="s">
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="I10" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="J10" s="39" t="s">
+      <c r="J10" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="K10" s="43">
+      <c r="K10" s="35">
         <v>650000</v>
       </c>
-      <c r="L10" s="44" t="s">
+      <c r="L10" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="M10" s="44"/>
-      <c r="N10" s="44"/>
-      <c r="P10" s="45" t="s">
+      <c r="M10" s="43"/>
+      <c r="N10" s="43"/>
+      <c r="P10" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="Q10" s="39" t="s">
+      <c r="Q10" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="R10" s="46">
+      <c r="R10" s="37">
         <v>440000</v>
       </c>
-      <c r="S10" s="44" t="s">
+      <c r="S10" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="T10" s="44"/>
-      <c r="U10" s="44"/>
+      <c r="T10" s="43"/>
+      <c r="U10" s="43"/>
     </row>
     <row r="11" spans="2:21" ht="60" x14ac:dyDescent="0.25">
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="D11" s="46">
+      <c r="D11" s="37">
         <v>420000</v>
       </c>
-      <c r="E11" s="44" t="s">
+      <c r="E11" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="F11" s="44"/>
-      <c r="G11" s="44"/>
-      <c r="I11" s="42" t="s">
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="I11" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="J11" s="39" t="s">
+      <c r="J11" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="K11" s="43">
+      <c r="K11" s="35">
         <v>420000</v>
       </c>
-      <c r="L11" s="44" t="s">
+      <c r="L11" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="M11" s="44"/>
-      <c r="N11" s="44"/>
-      <c r="P11" s="45" t="s">
+      <c r="M11" s="43"/>
+      <c r="N11" s="43"/>
+      <c r="P11" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="Q11" s="39" t="s">
+      <c r="Q11" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="R11" s="46">
+      <c r="R11" s="37">
         <v>425000</v>
       </c>
-      <c r="S11" s="44" t="s">
+      <c r="S11" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="T11" s="44"/>
-      <c r="U11" s="44"/>
+      <c r="T11" s="43"/>
+      <c r="U11" s="43"/>
     </row>
     <row r="12" spans="2:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="46">
+      <c r="D12" s="37">
         <v>185000</v>
       </c>
-      <c r="E12" s="44" t="s">
+      <c r="E12" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="I12" s="42" t="s">
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="I12" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="J12" s="39" t="s">
+      <c r="J12" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="K12" s="43">
+      <c r="K12" s="35">
         <v>185000</v>
       </c>
-      <c r="L12" s="44" t="s">
+      <c r="L12" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="M12" s="44"/>
-      <c r="N12" s="44"/>
-      <c r="P12" s="45" t="s">
+      <c r="M12" s="43"/>
+      <c r="N12" s="43"/>
+      <c r="P12" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="Q12" s="39" t="s">
+      <c r="Q12" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="R12" s="46">
+      <c r="R12" s="37">
         <v>185000</v>
       </c>
-      <c r="S12" s="44" t="s">
+      <c r="S12" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="T12" s="44"/>
-      <c r="U12" s="44"/>
+      <c r="T12" s="43"/>
+      <c r="U12" s="43"/>
     </row>
     <row r="13" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="C13" s="52" t="s">
+      <c r="C13" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="53">
+      <c r="D13" s="40">
         <v>6880000</v>
       </c>
-      <c r="J13" s="42" t="s">
+      <c r="J13" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="K13" s="43">
+      <c r="K13" s="35">
         <v>5050000</v>
       </c>
-      <c r="Q13" s="54" t="s">
+      <c r="Q13" s="41" t="s">
         <v>78</v>
       </c>
-      <c r="R13" s="46">
+      <c r="R13" s="37">
         <v>4856000</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="S12:U12"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="S8:U8"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="S9:U9"/>
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="S10:U10"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="J4:N4"/>
-    <mergeCell ref="Q4:U4"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="S5:U5"/>
     <mergeCell ref="E6:G6"/>
     <mergeCell ref="E11:G11"/>
     <mergeCell ref="L11:N11"/>
@@ -1865,6 +1849,22 @@
     <mergeCell ref="E8:G8"/>
     <mergeCell ref="L6:N6"/>
     <mergeCell ref="S6:U6"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="J4:N4"/>
+    <mergeCell ref="Q4:U4"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="S5:U5"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="S12:U12"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="S8:U8"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="S9:U9"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="S10:U10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/trimestre 2/CostosFichas.xlsx
+++ b/trimestre 2/CostosFichas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aprendiz\Desktop\XD\RoyalPets\trimestre 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E19219F-EDA0-469F-9411-7345D32BBC55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB2C5BF2-08EE-4580-8687-7FC4303E476B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E11BA5A1-A161-48B3-A771-26A7DBB69ABE}"/>
   </bookViews>
@@ -536,9 +536,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -572,27 +569,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -601,17 +580,11 @@
     </xf>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -619,26 +592,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1035,14 +1035,14 @@
     <col min="4" max="4" width="17.140625" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="22.5703125" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" customWidth="1"/>
+    <col min="7" max="7" width="27.5703125" customWidth="1"/>
     <col min="8" max="8" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="2:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1148,291 +1148,291 @@
       <c r="E7" s="1"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
       <c r="E8" s="1"/>
     </row>
     <row r="9" spans="2:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="17" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="19">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="20">
         <f>E$3*C10</f>
         <v>255000.00000000003</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="20">
         <f>E$4*C10</f>
         <v>238000.00000000003</v>
       </c>
-      <c r="F10" s="21">
+      <c r="F10" s="20">
         <f>E$5*C10</f>
         <v>297500</v>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="20">
         <f>E$6*C10</f>
         <v>153000</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="21">
         <v>0.12</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="20">
         <f t="shared" ref="D11:D19" si="0">E$3*C11</f>
         <v>360000</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="20">
         <f t="shared" ref="E11:E19" si="1">E$4*C11</f>
         <v>336000</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="20">
         <f t="shared" ref="F11:F19" si="2">E$5*C11</f>
         <v>420000</v>
       </c>
-      <c r="G11" s="21">
+      <c r="G11" s="20">
         <f t="shared" ref="G11:G19" si="3">E$6*C11</f>
         <v>216000</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="23">
+      <c r="C12" s="22">
         <v>5.2199999999999998E-3</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="20">
         <f t="shared" si="0"/>
         <v>15660</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="20">
         <f t="shared" si="1"/>
         <v>14616</v>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="20">
         <f t="shared" si="2"/>
         <v>18270</v>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="20">
         <f t="shared" si="3"/>
         <v>9396</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="24">
         <v>0.04</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="20">
         <f t="shared" si="0"/>
         <v>120000</v>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="20">
         <f t="shared" si="1"/>
         <v>112000</v>
       </c>
-      <c r="F13" s="21">
+      <c r="F13" s="20">
         <f t="shared" si="2"/>
         <v>140000</v>
       </c>
-      <c r="G13" s="21">
+      <c r="G13" s="20">
         <f t="shared" si="3"/>
         <v>72000</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="21">
         <v>0.02</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="20">
         <f t="shared" si="0"/>
         <v>60000</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="20">
         <f t="shared" si="1"/>
         <v>56000</v>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="20">
         <f t="shared" si="2"/>
         <v>70000</v>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="20">
         <f t="shared" si="3"/>
         <v>36000</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="21">
         <v>0.03</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="20">
         <f t="shared" si="0"/>
         <v>90000</v>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="20">
         <f t="shared" si="1"/>
         <v>84000</v>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="20">
         <f t="shared" si="2"/>
         <v>105000</v>
       </c>
-      <c r="G15" s="21">
+      <c r="G15" s="20">
         <f t="shared" si="3"/>
         <v>54000</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="25">
         <v>8.3299999999999999E-2</v>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="20">
         <f>E$3*C16</f>
         <v>249900</v>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="20">
         <f t="shared" si="1"/>
         <v>233240</v>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="20">
         <f t="shared" si="2"/>
         <v>291550</v>
       </c>
-      <c r="G16" s="21">
+      <c r="G16" s="20">
         <f t="shared" si="3"/>
         <v>149940</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="26">
         <v>8.3299999999999999E-2</v>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="20">
         <f t="shared" si="0"/>
         <v>249900</v>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="20">
         <f t="shared" si="1"/>
         <v>233240</v>
       </c>
-      <c r="F17" s="21">
+      <c r="F17" s="20">
         <f t="shared" si="2"/>
         <v>291550</v>
       </c>
-      <c r="G17" s="21">
+      <c r="G17" s="20">
         <f t="shared" si="3"/>
         <v>149940</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="22">
+      <c r="C18" s="21">
         <v>0.01</v>
       </c>
-      <c r="D18" s="21">
+      <c r="D18" s="20">
         <f t="shared" si="0"/>
         <v>30000</v>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="20">
         <f t="shared" si="1"/>
         <v>28000</v>
       </c>
-      <c r="F18" s="21">
+      <c r="F18" s="20">
         <f t="shared" si="2"/>
         <v>35000</v>
       </c>
-      <c r="G18" s="21">
+      <c r="G18" s="20">
         <f t="shared" si="3"/>
         <v>18000</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="26">
         <v>4.1700000000000001E-2</v>
       </c>
-      <c r="D19" s="21">
+      <c r="D19" s="20">
         <f t="shared" si="0"/>
         <v>125100</v>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="20">
         <f t="shared" si="1"/>
         <v>116760</v>
       </c>
-      <c r="F19" s="21">
+      <c r="F19" s="20">
         <f t="shared" si="2"/>
         <v>145950</v>
       </c>
-      <c r="G19" s="21">
+      <c r="G19" s="20">
         <f t="shared" si="3"/>
         <v>75060</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="21">
+      <c r="C20" s="26"/>
+      <c r="D20" s="20">
         <f>SUM(D10:D19)</f>
         <v>1555560</v>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="20">
         <f t="shared" ref="E20" si="4">SUM(E10:E19)</f>
         <v>1451856</v>
       </c>
-      <c r="F20" s="21">
+      <c r="F20" s="20">
         <f>SUM(F10+F11+F12+F13+F14+F15+F16+F17+F19+F18)</f>
         <v>1814820</v>
       </c>
-      <c r="G20" s="21">
+      <c r="G20" s="20">
         <f>SUM(G10+G11+G12+G13+G14+G15+G16+G17+G19+G18)</f>
         <v>933336</v>
       </c>
@@ -1451,409 +1451,393 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="4" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="J4" s="30" t="s">
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="J4" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="Q4" s="31" t="s">
+      <c r="K4" s="53"/>
+      <c r="L4" s="53"/>
+      <c r="M4" s="53"/>
+      <c r="N4" s="53"/>
+      <c r="Q4" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="R4" s="31"/>
-      <c r="S4" s="31"/>
-      <c r="T4" s="31"/>
-      <c r="U4" s="31"/>
+      <c r="R4" s="54"/>
+      <c r="S4" s="54"/>
+      <c r="T4" s="54"/>
+      <c r="U4" s="54"/>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="E5" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="J5" s="34" t="s">
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="J5" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="K5" s="34" t="s">
+      <c r="K5" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="L5" s="35" t="s">
+      <c r="L5" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="M5" s="35"/>
-      <c r="N5" s="35"/>
-      <c r="Q5" s="36" t="s">
+      <c r="M5" s="48"/>
+      <c r="N5" s="48"/>
+      <c r="Q5" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="R5" s="36" t="s">
+      <c r="R5" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="S5" s="37" t="s">
+      <c r="S5" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="T5" s="37"/>
-      <c r="U5" s="37"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
     </row>
     <row r="6" spans="2:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="39" t="s">
+      <c r="C6" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="40">
+      <c r="D6" s="33">
         <v>1196883</v>
       </c>
-      <c r="E6" s="41" t="s">
+      <c r="E6" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="I6" s="42" t="s">
+      <c r="F6" s="50"/>
+      <c r="G6" s="50"/>
+      <c r="I6" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="39" t="s">
+      <c r="J6" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="K6" s="43">
+      <c r="K6" s="35">
         <v>1196883</v>
       </c>
-      <c r="L6" s="44" t="s">
+      <c r="L6" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="M6" s="44"/>
-      <c r="N6" s="44"/>
-      <c r="P6" s="45" t="s">
+      <c r="M6" s="43"/>
+      <c r="N6" s="43"/>
+      <c r="P6" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="Q6" s="39" t="s">
+      <c r="Q6" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="R6" s="46">
+      <c r="R6" s="37">
         <v>1213134</v>
       </c>
-      <c r="S6" s="44" t="s">
+      <c r="S6" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="44"/>
-      <c r="U6" s="44"/>
+      <c r="T6" s="43"/>
+      <c r="U6" s="43"/>
     </row>
     <row r="7" spans="2:21" ht="75" x14ac:dyDescent="0.25">
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="39" t="s">
+      <c r="C7" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="40">
+      <c r="D7" s="33">
         <v>1834000</v>
       </c>
-      <c r="E7" s="44" t="s">
+      <c r="E7" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="I7" s="42" t="s">
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="I7" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="J7" s="47" t="s">
+      <c r="J7" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="K7" s="39" t="s">
+      <c r="K7" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="L7" s="48" t="s">
+      <c r="L7" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="M7" s="48"/>
-      <c r="N7" s="48"/>
-      <c r="P7" s="45" t="s">
+      <c r="M7" s="51"/>
+      <c r="N7" s="51"/>
+      <c r="P7" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="Q7" s="39" t="s">
+      <c r="Q7" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="R7" s="39" t="s">
+      <c r="R7" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="S7" s="48" t="s">
+      <c r="S7" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="T7" s="48"/>
-      <c r="U7" s="48"/>
+      <c r="T7" s="51"/>
+      <c r="U7" s="51"/>
     </row>
     <row r="8" spans="2:21" ht="75" x14ac:dyDescent="0.25">
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="39" t="s">
+      <c r="C8" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="43">
+      <c r="D8" s="35">
         <v>1600000</v>
       </c>
-      <c r="E8" s="44" t="s">
+      <c r="E8" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="I8" s="42" t="s">
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="I8" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="J8" s="39" t="s">
+      <c r="J8" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="K8" s="43">
+      <c r="K8" s="35">
         <v>1600000</v>
       </c>
-      <c r="L8" s="44" t="s">
+      <c r="L8" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="M8" s="44"/>
-      <c r="N8" s="44"/>
-      <c r="P8" s="45" t="s">
+      <c r="M8" s="43"/>
+      <c r="N8" s="43"/>
+      <c r="P8" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="Q8" s="39" t="s">
+      <c r="Q8" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="R8" s="46">
+      <c r="R8" s="37">
         <v>1600000</v>
       </c>
-      <c r="S8" s="44" t="s">
+      <c r="S8" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="T8" s="44"/>
-      <c r="U8" s="44"/>
+      <c r="T8" s="43"/>
+      <c r="U8" s="43"/>
     </row>
     <row r="9" spans="2:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="43">
+      <c r="D9" s="35">
         <v>996959</v>
       </c>
-      <c r="E9" s="49" t="s">
+      <c r="E9" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="50"/>
-      <c r="G9" s="51"/>
-      <c r="I9" s="42" t="s">
+      <c r="F9" s="45"/>
+      <c r="G9" s="46"/>
+      <c r="I9" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="J9" s="39" t="s">
+      <c r="J9" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="K9" s="43">
+      <c r="K9" s="35">
         <v>996959</v>
       </c>
-      <c r="L9" s="44" t="s">
+      <c r="L9" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="M9" s="44"/>
-      <c r="N9" s="44"/>
-      <c r="P9" s="45" t="s">
+      <c r="M9" s="43"/>
+      <c r="N9" s="43"/>
+      <c r="P9" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="Q9" s="39" t="s">
+      <c r="Q9" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="R9" s="46">
+      <c r="R9" s="37">
         <v>996959</v>
       </c>
-      <c r="S9" s="44" t="s">
+      <c r="S9" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="T9" s="44"/>
-      <c r="U9" s="44"/>
+      <c r="T9" s="43"/>
+      <c r="U9" s="43"/>
     </row>
     <row r="10" spans="2:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="43">
+      <c r="D10" s="35">
         <v>650000</v>
       </c>
-      <c r="E10" s="44" t="s">
+      <c r="E10" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="I10" s="42" t="s">
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="I10" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="J10" s="39" t="s">
+      <c r="J10" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="K10" s="43">
+      <c r="K10" s="35">
         <v>650000</v>
       </c>
-      <c r="L10" s="44" t="s">
+      <c r="L10" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="M10" s="44"/>
-      <c r="N10" s="44"/>
-      <c r="P10" s="45" t="s">
+      <c r="M10" s="43"/>
+      <c r="N10" s="43"/>
+      <c r="P10" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="Q10" s="39" t="s">
+      <c r="Q10" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="R10" s="46">
+      <c r="R10" s="37">
         <v>440000</v>
       </c>
-      <c r="S10" s="44" t="s">
+      <c r="S10" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="T10" s="44"/>
-      <c r="U10" s="44"/>
+      <c r="T10" s="43"/>
+      <c r="U10" s="43"/>
     </row>
     <row r="11" spans="2:21" ht="60" x14ac:dyDescent="0.25">
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="D11" s="46">
+      <c r="D11" s="37">
         <v>420000</v>
       </c>
-      <c r="E11" s="44" t="s">
+      <c r="E11" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="F11" s="44"/>
-      <c r="G11" s="44"/>
-      <c r="I11" s="42" t="s">
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="I11" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="J11" s="39" t="s">
+      <c r="J11" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="K11" s="43">
+      <c r="K11" s="35">
         <v>420000</v>
       </c>
-      <c r="L11" s="44" t="s">
+      <c r="L11" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="M11" s="44"/>
-      <c r="N11" s="44"/>
-      <c r="P11" s="45" t="s">
+      <c r="M11" s="43"/>
+      <c r="N11" s="43"/>
+      <c r="P11" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="Q11" s="39" t="s">
+      <c r="Q11" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="R11" s="46">
+      <c r="R11" s="37">
         <v>425000</v>
       </c>
-      <c r="S11" s="44" t="s">
+      <c r="S11" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="T11" s="44"/>
-      <c r="U11" s="44"/>
+      <c r="T11" s="43"/>
+      <c r="U11" s="43"/>
     </row>
     <row r="12" spans="2:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="46">
+      <c r="D12" s="37">
         <v>185000</v>
       </c>
-      <c r="E12" s="44" t="s">
+      <c r="E12" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="I12" s="42" t="s">
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="I12" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="J12" s="39" t="s">
+      <c r="J12" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="K12" s="43">
+      <c r="K12" s="35">
         <v>185000</v>
       </c>
-      <c r="L12" s="44" t="s">
+      <c r="L12" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="M12" s="44"/>
-      <c r="N12" s="44"/>
-      <c r="P12" s="45" t="s">
+      <c r="M12" s="43"/>
+      <c r="N12" s="43"/>
+      <c r="P12" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="Q12" s="39" t="s">
+      <c r="Q12" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="R12" s="46">
+      <c r="R12" s="37">
         <v>185000</v>
       </c>
-      <c r="S12" s="44" t="s">
+      <c r="S12" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="T12" s="44"/>
-      <c r="U12" s="44"/>
+      <c r="T12" s="43"/>
+      <c r="U12" s="43"/>
     </row>
     <row r="13" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="C13" s="52" t="s">
+      <c r="C13" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="53">
+      <c r="D13" s="40">
         <v>6880000</v>
       </c>
-      <c r="J13" s="42" t="s">
+      <c r="J13" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="K13" s="43">
+      <c r="K13" s="35">
         <v>5050000</v>
       </c>
-      <c r="Q13" s="54" t="s">
+      <c r="Q13" s="41" t="s">
         <v>78</v>
       </c>
-      <c r="R13" s="46">
+      <c r="R13" s="37">
         <v>4856000</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="S12:U12"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="S8:U8"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="S9:U9"/>
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="S10:U10"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="J4:N4"/>
-    <mergeCell ref="Q4:U4"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="S5:U5"/>
     <mergeCell ref="E6:G6"/>
     <mergeCell ref="E11:G11"/>
     <mergeCell ref="L11:N11"/>
@@ -1865,6 +1849,22 @@
     <mergeCell ref="E8:G8"/>
     <mergeCell ref="L6:N6"/>
     <mergeCell ref="S6:U6"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="J4:N4"/>
+    <mergeCell ref="Q4:U4"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="S5:U5"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="S12:U12"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="S8:U8"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="S9:U9"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="S10:U10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/trimestre 2/CostosFichas.xlsx
+++ b/trimestre 2/CostosFichas.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aprendiz\Desktop\XD\RoyalPets\trimestre 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB2C5BF2-08EE-4580-8687-7FC4303E476B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C44E865-81C7-4CE2-9F12-1A3BEEE5B226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E11BA5A1-A161-48B3-A771-26A7DBB69ABE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E11BA5A1-A161-48B3-A771-26A7DBB69ABE}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
+    <sheet name="Personal" sheetId="1" r:id="rId1"/>
+    <sheet name="equipos" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -605,7 +605,31 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -615,30 +639,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1451,27 +1451,27 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="4" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="C4" s="52" t="s">
+      <c r="C4" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="J4" s="53" t="s">
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="J4" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="K4" s="53"/>
-      <c r="L4" s="53"/>
-      <c r="M4" s="53"/>
-      <c r="N4" s="53"/>
-      <c r="Q4" s="54" t="s">
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="47"/>
+      <c r="N4" s="47"/>
+      <c r="Q4" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="R4" s="54"/>
-      <c r="S4" s="54"/>
-      <c r="T4" s="54"/>
-      <c r="U4" s="54"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.25">
       <c r="C5" s="28" t="s">
@@ -1480,33 +1480,33 @@
       <c r="D5" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="47" t="s">
+      <c r="E5" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
       <c r="J5" s="29" t="s">
         <v>34</v>
       </c>
       <c r="K5" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="L5" s="48" t="s">
+      <c r="L5" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="M5" s="48"/>
-      <c r="N5" s="48"/>
+      <c r="M5" s="50"/>
+      <c r="N5" s="50"/>
       <c r="Q5" s="30" t="s">
         <v>34</v>
       </c>
       <c r="R5" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="S5" s="49" t="s">
+      <c r="S5" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
+      <c r="T5" s="51"/>
+      <c r="U5" s="51"/>
     </row>
     <row r="6" spans="2:21" ht="30" x14ac:dyDescent="0.25">
       <c r="B6" s="31" t="s">
@@ -1518,11 +1518,11 @@
       <c r="D6" s="33">
         <v>1196883</v>
       </c>
-      <c r="E6" s="50" t="s">
+      <c r="E6" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
       <c r="I6" s="34" t="s">
         <v>37</v>
       </c>
@@ -1532,11 +1532,11 @@
       <c r="K6" s="35">
         <v>1196883</v>
       </c>
-      <c r="L6" s="43" t="s">
+      <c r="L6" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="M6" s="43"/>
-      <c r="N6" s="43"/>
+      <c r="M6" s="44"/>
+      <c r="N6" s="44"/>
       <c r="P6" s="36" t="s">
         <v>37</v>
       </c>
@@ -1546,11 +1546,11 @@
       <c r="R6" s="37">
         <v>1213134</v>
       </c>
-      <c r="S6" s="43" t="s">
+      <c r="S6" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="43"/>
-      <c r="U6" s="43"/>
+      <c r="T6" s="44"/>
+      <c r="U6" s="44"/>
     </row>
     <row r="7" spans="2:21" ht="75" x14ac:dyDescent="0.25">
       <c r="B7" s="31" t="s">
@@ -1562,11 +1562,11 @@
       <c r="D7" s="33">
         <v>1834000</v>
       </c>
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="43"/>
-      <c r="G7" s="43"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
       <c r="I7" s="34" t="s">
         <v>43</v>
       </c>
@@ -1576,11 +1576,11 @@
       <c r="K7" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="L7" s="51" t="s">
+      <c r="L7" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="M7" s="51"/>
-      <c r="N7" s="51"/>
+      <c r="M7" s="45"/>
+      <c r="N7" s="45"/>
       <c r="P7" s="36" t="s">
         <v>43</v>
       </c>
@@ -1590,11 +1590,11 @@
       <c r="R7" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="S7" s="51" t="s">
+      <c r="S7" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="T7" s="51"/>
-      <c r="U7" s="51"/>
+      <c r="T7" s="45"/>
+      <c r="U7" s="45"/>
     </row>
     <row r="8" spans="2:21" ht="75" x14ac:dyDescent="0.25">
       <c r="B8" s="31" t="s">
@@ -1606,11 +1606,11 @@
       <c r="D8" s="35">
         <v>1600000</v>
       </c>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
       <c r="I8" s="34" t="s">
         <v>47</v>
       </c>
@@ -1620,11 +1620,11 @@
       <c r="K8" s="35">
         <v>1600000</v>
       </c>
-      <c r="L8" s="43" t="s">
+      <c r="L8" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="M8" s="43"/>
-      <c r="N8" s="43"/>
+      <c r="M8" s="44"/>
+      <c r="N8" s="44"/>
       <c r="P8" s="36" t="s">
         <v>47</v>
       </c>
@@ -1634,11 +1634,11 @@
       <c r="R8" s="37">
         <v>1600000</v>
       </c>
-      <c r="S8" s="43" t="s">
+      <c r="S8" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="T8" s="43"/>
-      <c r="U8" s="43"/>
+      <c r="T8" s="44"/>
+      <c r="U8" s="44"/>
     </row>
     <row r="9" spans="2:21" ht="45" x14ac:dyDescent="0.25">
       <c r="B9" s="31" t="s">
@@ -1650,11 +1650,11 @@
       <c r="D9" s="35">
         <v>996959</v>
       </c>
-      <c r="E9" s="44" t="s">
+      <c r="E9" s="52" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="45"/>
-      <c r="G9" s="46"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="54"/>
       <c r="I9" s="34" t="s">
         <v>54</v>
       </c>
@@ -1664,11 +1664,11 @@
       <c r="K9" s="35">
         <v>996959</v>
       </c>
-      <c r="L9" s="43" t="s">
+      <c r="L9" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="M9" s="43"/>
-      <c r="N9" s="43"/>
+      <c r="M9" s="44"/>
+      <c r="N9" s="44"/>
       <c r="P9" s="36" t="s">
         <v>54</v>
       </c>
@@ -1678,11 +1678,11 @@
       <c r="R9" s="37">
         <v>996959</v>
       </c>
-      <c r="S9" s="43" t="s">
+      <c r="S9" s="44" t="s">
         <v>58</v>
       </c>
-      <c r="T9" s="43"/>
-      <c r="U9" s="43"/>
+      <c r="T9" s="44"/>
+      <c r="U9" s="44"/>
     </row>
     <row r="10" spans="2:21" ht="45" x14ac:dyDescent="0.25">
       <c r="B10" s="31" t="s">
@@ -1694,11 +1694,11 @@
       <c r="D10" s="35">
         <v>650000</v>
       </c>
-      <c r="E10" s="43" t="s">
+      <c r="E10" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F10" s="43"/>
-      <c r="G10" s="43"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
       <c r="I10" s="34" t="s">
         <v>59</v>
       </c>
@@ -1708,11 +1708,11 @@
       <c r="K10" s="35">
         <v>650000</v>
       </c>
-      <c r="L10" s="43" t="s">
+      <c r="L10" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="M10" s="43"/>
-      <c r="N10" s="43"/>
+      <c r="M10" s="44"/>
+      <c r="N10" s="44"/>
       <c r="P10" s="36" t="s">
         <v>59</v>
       </c>
@@ -1722,11 +1722,11 @@
       <c r="R10" s="37">
         <v>440000</v>
       </c>
-      <c r="S10" s="43" t="s">
+      <c r="S10" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="T10" s="43"/>
-      <c r="U10" s="43"/>
+      <c r="T10" s="44"/>
+      <c r="U10" s="44"/>
     </row>
     <row r="11" spans="2:21" ht="60" x14ac:dyDescent="0.25">
       <c r="B11" s="31" t="s">
@@ -1738,11 +1738,11 @@
       <c r="D11" s="37">
         <v>420000</v>
       </c>
-      <c r="E11" s="43" t="s">
+      <c r="E11" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
       <c r="I11" s="34" t="s">
         <v>65</v>
       </c>
@@ -1752,11 +1752,11 @@
       <c r="K11" s="35">
         <v>420000</v>
       </c>
-      <c r="L11" s="43" t="s">
+      <c r="L11" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="M11" s="43"/>
-      <c r="N11" s="43"/>
+      <c r="M11" s="44"/>
+      <c r="N11" s="44"/>
       <c r="P11" s="36" t="s">
         <v>65</v>
       </c>
@@ -1766,11 +1766,11 @@
       <c r="R11" s="37">
         <v>425000</v>
       </c>
-      <c r="S11" s="43" t="s">
+      <c r="S11" s="44" t="s">
         <v>71</v>
       </c>
-      <c r="T11" s="43"/>
-      <c r="U11" s="43"/>
+      <c r="T11" s="44"/>
+      <c r="U11" s="44"/>
     </row>
     <row r="12" spans="2:21" ht="45" x14ac:dyDescent="0.25">
       <c r="B12" s="31" t="s">
@@ -1782,11 +1782,11 @@
       <c r="D12" s="37">
         <v>185000</v>
       </c>
-      <c r="E12" s="43" t="s">
+      <c r="E12" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
       <c r="I12" s="34" t="s">
         <v>72</v>
       </c>
@@ -1796,11 +1796,11 @@
       <c r="K12" s="35">
         <v>185000</v>
       </c>
-      <c r="L12" s="43" t="s">
+      <c r="L12" s="44" t="s">
         <v>76</v>
       </c>
-      <c r="M12" s="43"/>
-      <c r="N12" s="43"/>
+      <c r="M12" s="44"/>
+      <c r="N12" s="44"/>
       <c r="P12" s="36" t="s">
         <v>72</v>
       </c>
@@ -1810,11 +1810,11 @@
       <c r="R12" s="37">
         <v>185000</v>
       </c>
-      <c r="S12" s="43" t="s">
+      <c r="S12" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="T12" s="43"/>
-      <c r="U12" s="43"/>
+      <c r="T12" s="44"/>
+      <c r="U12" s="44"/>
     </row>
     <row r="13" spans="2:21" x14ac:dyDescent="0.25">
       <c r="C13" s="39" t="s">
@@ -1838,6 +1838,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="S9:U9"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="S10:U10"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="J4:N4"/>
+    <mergeCell ref="Q4:U4"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="S5:U5"/>
     <mergeCell ref="E6:G6"/>
     <mergeCell ref="E11:G11"/>
     <mergeCell ref="L11:N11"/>
@@ -1849,22 +1860,11 @@
     <mergeCell ref="E8:G8"/>
     <mergeCell ref="L6:N6"/>
     <mergeCell ref="S6:U6"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="J4:N4"/>
-    <mergeCell ref="Q4:U4"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="S5:U5"/>
     <mergeCell ref="L12:N12"/>
     <mergeCell ref="S12:U12"/>
     <mergeCell ref="L8:N8"/>
     <mergeCell ref="S8:U8"/>
     <mergeCell ref="E9:G9"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="S9:U9"/>
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="S10:U10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
